--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738074</v>
       </c>
       <c r="B2" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131740727</v>
       </c>
       <c r="B3" t="n">
-        <v>83240</v>
+        <v>83241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738074</v>
       </c>
       <c r="B2" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131740727</v>
       </c>
       <c r="B3" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738074</v>
       </c>
       <c r="B2" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131740727</v>
       </c>
       <c r="B3" t="n">
-        <v>83244</v>
+        <v>83246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738074</v>
       </c>
       <c r="B2" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131740727</v>
       </c>
       <c r="B3" t="n">
-        <v>83246</v>
+        <v>83249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738074</v>
       </c>
       <c r="B2" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131740727</v>
       </c>
       <c r="B3" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738074</v>
       </c>
       <c r="B2" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131740727</v>
       </c>
       <c r="B3" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131738074</v>
       </c>
       <c r="B2" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131740727</v>
       </c>
       <c r="B3" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131738074</v>
+        <v>131740727</v>
       </c>
       <c r="B2" t="n">
-        <v>80422</v>
+        <v>83358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarndammet Nordväst, Vb</t>
+          <t>Kvarndammet Väst, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>731016</v>
+        <v>731034</v>
       </c>
       <c r="R2" t="n">
-        <v>7184792</v>
+        <v>7184814</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131740727</v>
+        <v>131738074</v>
       </c>
       <c r="B3" t="n">
-        <v>83297</v>
+        <v>80488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarndammet Väst, Vb</t>
+          <t>Kvarndammet Nordväst, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>731034</v>
+        <v>731016</v>
       </c>
       <c r="R3" t="n">
-        <v>7184814</v>
+        <v>7184792</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +870,107 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131740207</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kvarndammet Nordväst, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>731048</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7184777</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740727</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738074</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740207</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131740727</v>
+        <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>83358</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarndammet Väst, Vb</t>
+          <t>Kvarndammet, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>731034</v>
+        <v>731035</v>
       </c>
       <c r="R2" t="n">
-        <v>7184814</v>
+        <v>7184689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,37 +766,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131740727</t>
+          <t>https://artportalen.se/Sighting/136247024</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131738074</v>
+        <v>136247735</v>
       </c>
       <c r="B3" t="n">
-        <v>80488</v>
+        <v>83311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,34 +801,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarndammet Nordväst, Vb</t>
+          <t>Kvarndammet, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>731016</v>
+        <v>730976</v>
       </c>
       <c r="R3" t="n">
-        <v>7184792</v>
+        <v>7184699</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,72 +876,76 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131738074</t>
+          <t>https://artportalen.se/Sighting/136247735</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131740207</v>
+        <v>136247010</v>
       </c>
       <c r="B4" t="n">
-        <v>79396</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>260591</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarndammet Nordväst, Vb</t>
+          <t>Kvarndammet, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>731048</v>
+        <v>731016</v>
       </c>
       <c r="R4" t="n">
-        <v>7184777</v>
+        <v>7184672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,28 +986,2499 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136247010</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136248059</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79444</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>730965</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7184737</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248059</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136248070</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79444</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>730987</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7184770</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248070</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136248188</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79444</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>731066</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7184833</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248188</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131740727</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kvarndammet Väst, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>731034</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7184814</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Elin Kollberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740727</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131738074</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kvarndammet Nordväst, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>731016</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7184792</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738074</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136248140</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80559</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>731024</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7184831</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>rikligt på en gammal sälg</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248140</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136248274</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80570</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>731019</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7184708</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248274</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136248242</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>731046</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7184808</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>hackade hål i gammal gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248242</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136247961</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>730962</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7184702</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136247961</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136247996</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>730966</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7184697</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136247996</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136248020</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>730959</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7184699</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248020</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136248030</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>730948</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7184693</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248030</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136248045</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>730973</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7184727</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248045</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136248055</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>730973</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7184737</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248055</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136248076</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>731013</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7184817</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>gamla ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248076</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136248169</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>731066</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7184817</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248169</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136248204</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>731066</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7184807</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248204</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136248225</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>731054</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7184796</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248225</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136248261</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>731025</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7184703</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136248261</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136247941</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>730985</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7184707</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>karaktärisktiskt läte</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136247941</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131740207</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kvarndammet Nordväst, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>731048</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7184777</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131740207</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136247035</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92458</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kvarndammet, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>730998</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7184704</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136247035</t>
         </is>
       </c>
     </row>
@@ -1001,6 +3487,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136247735</v>
       </c>
       <c r="B3" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136247010</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136248059</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136248070</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136248188</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136248140</v>
       </c>
       <c r="B10" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136248274</v>
       </c>
       <c r="B11" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>136248242</v>
       </c>
       <c r="B12" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136247961</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>136247996</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136248020</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136248030</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>136248045</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>136248055</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136248076</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136248169</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136248204</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>136248225</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136248261</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>136247941</v>
       </c>
       <c r="B24" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92458</v>
+        <v>92459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136247735</v>
       </c>
       <c r="B3" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136247010</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136248059</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136248070</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136248188</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136248140</v>
       </c>
       <c r="B10" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136248274</v>
       </c>
       <c r="B11" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>136248242</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136247961</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>136247996</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136248020</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136248030</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>136248045</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>136248055</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136248076</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136248169</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136248204</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>136248225</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136248261</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>136247941</v>
       </c>
       <c r="B24" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92459</v>
+        <v>92465</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136247735</v>
       </c>
       <c r="B3" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136247010</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136248059</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136248070</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136248188</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136248140</v>
       </c>
       <c r="B10" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136248274</v>
       </c>
       <c r="B11" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>136248242</v>
       </c>
       <c r="B12" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136247961</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>136247996</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136248020</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136248030</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>136248045</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>136248055</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136248076</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136248169</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136248204</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>136248225</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136248261</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>136247941</v>
       </c>
       <c r="B24" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92465</v>
+        <v>92466</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136247735</v>
       </c>
       <c r="B3" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136247010</v>
       </c>
       <c r="B4" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136248059</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136248070</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136248188</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136248140</v>
       </c>
       <c r="B10" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136248274</v>
       </c>
       <c r="B11" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92466</v>
+        <v>92472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136247735</v>
       </c>
       <c r="B3" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136247010</v>
       </c>
       <c r="B4" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136248059</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136248070</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136248188</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136248140</v>
       </c>
       <c r="B10" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136248274</v>
       </c>
       <c r="B11" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>136248242</v>
       </c>
       <c r="B12" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136247961</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>136247996</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136248020</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136248030</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>136248045</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>136248055</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136248076</v>
       </c>
       <c r="B19" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136248169</v>
       </c>
       <c r="B20" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136248204</v>
       </c>
       <c r="B21" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>136248225</v>
       </c>
       <c r="B22" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136248261</v>
       </c>
       <c r="B23" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>136247941</v>
       </c>
       <c r="B24" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92472</v>
+        <v>92479</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92479</v>
+        <v>92480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136247735</v>
       </c>
       <c r="B3" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136247010</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136248059</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136248070</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136248188</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136248140</v>
       </c>
       <c r="B10" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136248274</v>
       </c>
       <c r="B11" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>136248242</v>
       </c>
       <c r="B12" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136247961</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>136247996</v>
       </c>
       <c r="B14" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136248020</v>
       </c>
       <c r="B15" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136248030</v>
       </c>
       <c r="B16" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>136248045</v>
       </c>
       <c r="B17" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>136248055</v>
       </c>
       <c r="B18" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136248076</v>
       </c>
       <c r="B19" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136248169</v>
       </c>
       <c r="B20" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136248204</v>
       </c>
       <c r="B21" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>136248225</v>
       </c>
       <c r="B22" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136248261</v>
       </c>
       <c r="B23" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>136247941</v>
       </c>
       <c r="B24" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92480</v>
+        <v>92493</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136247735</v>
       </c>
       <c r="B3" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136247010</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136248059</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136248070</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136248188</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136248140</v>
       </c>
       <c r="B10" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136248274</v>
       </c>
       <c r="B11" t="n">
-        <v>80599</v>
+        <v>80600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92493</v>
+        <v>92494</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
